--- a/sample_data/ENGG_backlog_2026-09.xlsx
+++ b/sample_data/ENGG_backlog_2026-09.xlsx
@@ -471,57 +471,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COR-MM-MRU</t>
+          <t>COR-SAL-CHCR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COR-MM-MRU-track</t>
+          <t>COR-SAL-CHCR-track</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-20 01:30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-09-20 04:20</t>
-        </is>
+        <v>3.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COR-NKJ-KTKD</t>
+          <t>COR-SZ-HWT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COR-NKJ-KTKD-track</t>
+          <t>COR-SZ-HWT-track</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,7 +535,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5.61</v>
+        <v>3.61</v>
       </c>
       <c r="H3" t="n">
         <v>30</v>
@@ -583,78 +573,71 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6.55</v>
+        <v>4.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-15 10:15</t>
+          <t>2026-09-14 10:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-15 16:48</t>
+          <t>2026-09-14 14:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COR-RU-TPTY</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COR-RU-TPTY-track</t>
+          <t>COR-RPK-GGD-track</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-09-17 23:00</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-09-18 01:33</t>
-        </is>
+        <v>3.61</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COR-MTI-TDL</t>
+          <t>COR-PTPU-TDD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COR-MTI-TDL-track</t>
+          <t>COR-PTPU-TDD-track</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -664,16 +647,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
         <v>30</v>
@@ -682,60 +665,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COR-DNDL-DNKL</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COR-DNDL-DNKL-track</t>
+          <t>COR-LBA-MWP-track</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="H7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:22</t>
-        </is>
+        <v>4.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COR-SJV-MANI</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COR-SJV-MANI-track</t>
+          <t>COR-BSR-JCNR-track</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -745,7 +715,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -755,21 +725,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-14 01:30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-09-14 05:43</t>
-        </is>
+        <v>2.43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +767,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4.28</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="10">
@@ -839,28 +802,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6.93</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COR-JSG-BXQ</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COR-JSG-BXQ-track</t>
+          <t>COR-LBA-MWP-track</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -870,25 +833,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H11" t="n">
-        <v>20</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COR-KUTI-BLPR</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COR-KUTI-BLPR-track</t>
+          <t>COR-BSR-JCNR-track</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -912,23 +872,23 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5.23</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COR-BIGA-SDGH</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COR-BIGA-SDGH-track</t>
+          <t>COR-KKRD-VYA-track</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -938,42 +898,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-09-12 06:03</t>
-        </is>
+        <v>3.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COR-KBI-LWR</t>
+          <t>COR-CGN-PIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COR-KBI-LWR-track</t>
+          <t>COR-CGN-PIC-track</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -988,11 +938,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5.58</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="15">
@@ -1027,18 +977,18 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6.32</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COR-NILE-DGLE</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COR-NILE-DGLE-track</t>
+          <t>COR-GNJ-KNP-track</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1062,7 +1012,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="H16" t="n">
         <v>20</v>
@@ -1071,67 +1021,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COR-NUD-VRR</t>
+          <t>COR-NTT-CJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COR-NUD-VRR-track</t>
+          <t>COR-NTT-CJ-track</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-09-20 22:00</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-09-21 05:13</t>
-        </is>
+        <v>2.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COR-SJSM-TIBI</t>
+          <t>COR-CGN-PIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COR-SJSM-TIBI-track</t>
+          <t>COR-CGN-PIC-track</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1141,62 +1081,65 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5.59</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COR-SRKI-MNV</t>
+          <t>COR-SNK-SNSL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COR-SRKI-MNV-track</t>
+          <t>COR-SNK-SNSL-track</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COR-LMA-MDL</t>
+          <t>COR-BBK-RES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COR-LMA-MDL-track</t>
+          <t>COR-BBK-RES-track</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1206,87 +1149,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-19 02:15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-09-19 07:27</t>
-        </is>
+        <v>1.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COR-SIRD-NKRA</t>
+          <t>COR-KRG-STR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COR-SIRD-NKRA-track</t>
+          <t>COR-KRG-STR-track</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COR-FSW-SDS</t>
+          <t>COR-LTT-CLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COR-FSW-SDS-track</t>
+          <t>COR-LTT-CLA-track</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1295,33 +1228,23 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:59</t>
-        </is>
+        <v>2.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COR-KAH-MABA</t>
+          <t>COR-TKC-PNB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COR-KAH-MABA-track</t>
+          <t>COR-TKC-PNB-track</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1331,40 +1254,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-14 01:30</t>
+          <t>2026-09-13 00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-14 03:54</t>
+          <t>2026-09-13 02:18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COR-DRR-RMY</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COR-DRR-RMY-track</t>
+          <t>COR-DMA-BURN-track</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1374,7 +1297,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1384,11 +1307,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1423,18 +1349,18 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.57</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COR-THL-MCN</t>
+          <t>COR-JU-BGKT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COR-THL-MCN-track</t>
+          <t>COR-JU-BGKT-track</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1444,7 +1370,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1454,135 +1380,135 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5.92</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COR-PATA-PHD</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COR-PATA-PHD-track</t>
+          <t>COR-RPK-GGD-track</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COR-STA-BGHI</t>
+          <t>COR-TKC-PNB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COR-STA-BGHI-track</t>
+          <t>COR-TKC-PNB-track</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="H28" t="n">
-        <v>15</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COR-OGL-SDM</t>
+          <t>COR-VHGN-WIRR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COR-OGL-SDM-track</t>
+          <t>COR-VHGN-WIRR-track</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>7.81</v>
+        <v>4.53</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COR-ALY-ALD</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COR-ALY-ALD-track</t>
+          <t>COR-KHDI-PDH-track</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1597,27 +1523,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7.19</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COR-BVNR-TKR</t>
+          <t>COR-NMDR-MPN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COR-BVNR-TKR-track</t>
+          <t>COR-NMDR-MPN-track</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1627,35 +1553,45 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3.71</v>
+        <v>4.08</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-13 00:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:04</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COR-NMDR-MPN</t>
+          <t>COR-RNL-DDE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COR-NMDR-MPN-track</t>
+          <t>COR-RNL-DDE-track</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1665,40 +1601,40 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6.41</v>
+        <v>1.74</v>
       </c>
       <c r="H32" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-12 00:00</t>
+          <t>2026-09-13 11:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-12 06:24</t>
+          <t>2026-09-13 12:44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COR-MMP-AND</t>
+          <t>COR-PUG-KLS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COR-MMP-AND-track</t>
+          <t>COR-PUG-KLS-track</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1713,32 +1649,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COR-THB-NNA</t>
+          <t>COR-IDJ-KNP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COR-THB-NNA-track</t>
+          <t>COR-IDJ-KNP-track</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1748,37 +1684,47 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4.42</v>
+        <v>2.43</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:40</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COR-PUG-KLS</t>
+          <t>COR-UMRI-BLSA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COR-PUG-KLS-track</t>
+          <t>COR-UMRI-BLSA-track</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1788,22 +1734,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4.52</v>
+        <v>1.76</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:00</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COR-IKR-PUX</t>
+          <t>COR-JRA-MOU</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COR-IKR-PUX-track</t>
+          <t>COR-JRA-MOU-track</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1818,42 +1774,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-09-16 14:15</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-09-16 17:50</t>
-        </is>
+        <v>3.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COR-UMRI-BLSA</t>
+          <t>COR-BGPR-JAL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COR-UMRI-BLSA-track</t>
+          <t>COR-BGPR-JAL-track</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1863,396 +1809,386 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2.44</v>
+        <v>4.79</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-16 02:15</t>
+          <t>2026-09-14 01:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-16 04:41</t>
+          <t>2026-09-14 06:17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COR-BMAE-DNHL</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COR-BMAE-DNHL-track</t>
+          <t>COR-GNJ-KNP-track</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COR-BGPR-JAL</t>
+          <t>COR-SNK-SNSL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COR-BGPR-JAL-track</t>
+          <t>COR-SNK-SNSL-track</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-09-13 09:07</t>
-        </is>
+        <v>3.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COR-TPW-TPTY</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COR-TPW-TPTY-track</t>
+          <t>COR-RPK-GGD-track</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3.22</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COR-GNS-TPNI</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COR-GNS-TPNI-track</t>
+          <t>COR-KHDI-PDH-track</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5.81</v>
+        <v>1.63</v>
+      </c>
+      <c r="H41" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COR-ATNR-DGA</t>
+          <t>COR-SZ-HWT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COR-ATNR-DGA-track</t>
+          <t>COR-SZ-HWT-track</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>7.88</v>
+        <v>2.24</v>
+      </c>
+      <c r="H42" t="n">
+        <v>20</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-19 11:30</t>
+          <t>2026-09-13 10:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-19 19:22</t>
+          <t>2026-09-13 12:44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COR-KSG-TL</t>
+          <t>COR-GNS-PDE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COR-KSG-TL-track</t>
+          <t>COR-GNS-PDE-track</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="H43" t="n">
-        <v>15</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COR-CHBN-TBX</t>
+          <t>COR-KHAT-RRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COR-CHBN-TBX-track</t>
+          <t>COR-KHAT-RRL-track</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="H44" t="n">
-        <v>15</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-09-12 08:38</t>
-        </is>
+        <v>4.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COR-GNS-PDE</t>
+          <t>COR-VVN-MYP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COR-GNS-PDE-track</t>
+          <t>COR-VVN-MYP-track</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7.86</v>
+        <v>4.55</v>
+      </c>
+      <c r="H45" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COR-CNX-JGA</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COR-CNX-JGA-track</t>
+          <t>COR-BSR-JCNR-track</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="H46" t="n">
-        <v>30</v>
+        <v>1.58</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:34</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COR-DGLE-NILE</t>
+          <t>COR-GPDE-SAP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COR-DGLE-NILE-track</t>
+          <t>COR-GPDE-SAP-track</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2262,72 +2198,85 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>7.23</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COR-MRA-SANK</t>
+          <t>COR-MGME-KLRE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COR-MRA-SANK-track</t>
+          <t>COR-MGME-KLRE-track</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
+      </c>
+      <c r="H48" t="n">
+        <v>15</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:05</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COR-MLY-CHZ</t>
+          <t>COR-RCGT-DEMU</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COR-MLY-CHZ-track</t>
+          <t>COR-RCGT-DEMU-track</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2337,223 +2286,217 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="H49" t="n">
-        <v>20</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-09-12 10:30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-09-12 14:10</t>
-        </is>
+        <v>1.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COR-RJAK-SPDM</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COR-RJAK-SPDM-track</t>
+          <t>COR-KBH-KHTG-track</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-16 02:30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-09-16 10:08</t>
-        </is>
+        <v>4.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COR-BHTL-BPKA</t>
+          <t>COR-NDD-BMGM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COR-BHTL-BPKA-track</t>
+          <t>COR-NDD-BMGM-track</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="H51" t="n">
-        <v>30</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COR-FKM-SPX</t>
+          <t>COR-BRLF-LMG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COR-FKM-SPX-track</t>
+          <t>COR-BRLF-LMG-track</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3.53</v>
+        <v>4.12</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-09-23 03:22</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COR-SKR-RNBD</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COR-SKR-RNBD-track</t>
+          <t>COR-KHDI-PDH-track</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6.32</v>
+        <v>3.62</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:30</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:07</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COR-GBK-KTJI</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COR-GBK-KTJI-track</t>
+          <t>COR-DXG-BHNE-track</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>5.74</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COR-NDD-BMGM</t>
+          <t>COR-TKC-PNB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COR-NDD-BMGM-track</t>
+          <t>COR-TKC-PNB-track</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2568,27 +2511,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3.96</v>
+        <v>1.59</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:50</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COR-BMF-MRV</t>
+          <t>COR-USD-DSD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COR-BMF-MRV-track</t>
+          <t>COR-USD-DSD-track</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2598,7 +2551,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2608,77 +2561,70 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6.49</v>
+        <v>2.9</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-21 23:15</t>
+          <t>2026-09-13 01:15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-22 05:44</t>
+          <t>2026-09-13 04:09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COR-VAR-JOO</t>
+          <t>COR-CUE-TISI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COR-VAR-JOO-track</t>
+          <t>COR-CUE-TISI-track</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-09-19 14:30</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-09-19 20:08</t>
-        </is>
+        <v>1.97</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COR-DDV-DKNT</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COR-DDV-DKNT-track</t>
+          <t>COR-KHTG-KBH-track</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2693,32 +2639,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2.51</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COR-SWNI-CRW</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COR-SWNI-CRW-track</t>
+          <t>COR-KHTG-KBH-track</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2728,115 +2674,102 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COR-MGKM-TLMR</t>
+          <t>COR-KLOD-SZH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COR-MGKM-TLMR-track</t>
+          <t>COR-KLOD-SZH-track</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="H60" t="n">
-        <v>15</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COR-KEJ-KANO</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COR-KEJ-KANO-track</t>
+          <t>COR-RPK-GGD-track</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-09-12 11:00</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-09-12 16:56</t>
-        </is>
+        <v>2.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COR-SRB-DRTP</t>
+          <t>COR-LKA-DHRY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COR-SRB-DRTP-track</t>
+          <t>COR-LKA-DHRY-track</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2846,167 +2779,167 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>7.5</v>
+        <v>3.13</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:30</t>
+          <t>2026-09-19 11:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-09-14 22:00</t>
+          <t>2026-09-19 14:37</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COR-TALA-KOAA</t>
+          <t>COR-MSW-SNC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COR-TALA-KOAA-track</t>
+          <t>COR-MSW-SNC-track</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6.98</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COR-KCU-BTRI</t>
+          <t>COR-STA-TZR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COR-KCU-BTRI-track</t>
+          <t>COR-STA-TZR-track</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:51</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COR-SGDP-CLDR</t>
+          <t>COR-TVNL-KDMD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COR-SGDP-CLDR-track</t>
+          <t>COR-TVNL-KDMD-track</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-09-16 01:00</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-09-16 04:24</t>
-        </is>
+        <v>2.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COR-DNR-NEO</t>
+          <t>COR-NBS-NCB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>COR-DNR-NEO-track</t>
+          <t>COR-NBS-NCB-track</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3015,18 +2948,31 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2.39</v>
+        <v>3.82</v>
+      </c>
+      <c r="H66" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-09-16 06:04</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COR-COE-AAR</t>
+          <t>COR-IDJ-KNP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COR-COE-AAR-track</t>
+          <t>COR-IDJ-KNP-track</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3036,45 +2982,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="H67" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:00</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:40</t>
-        </is>
+        <v>2.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COR-AJU-WDG</t>
+          <t>COR-JU-BGKT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COR-AJU-WDG-track</t>
+          <t>COR-JU-BGKT-track</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3089,42 +3022,52 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>6.49</v>
+        <v>4.12</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-09-19 02:37</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COR-KOA-MXS</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COR-KOA-MXS-track</t>
+          <t>COR-DMA-BURN-track</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3133,118 +3076,101 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2.17</v>
+        <v>3.67</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-18 02:15</t>
+          <t>2026-09-20 01:30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-09-18 04:25</t>
+          <t>2026-09-20 05:10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COR-IGU-SUU</t>
+          <t>COR-MGT-UTN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COR-IGU-SUU-track</t>
+          <t>COR-MGT-UTN-track</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-09-18 02:15</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-09-18 07:38</t>
-        </is>
+        <v>3.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COR-CBE-PTJ</t>
+          <t>COR-TIS-GAG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COR-CBE-PTJ-track</t>
+          <t>COR-TIS-GAG-track</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-09-18 23:15</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-09-19 03:58</t>
-        </is>
+        <v>3.87</v>
+      </c>
+      <c r="H71" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COR-GNB-KGI</t>
+          <t>COR-BRLF-LMG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COR-GNB-KGI-track</t>
+          <t>COR-BRLF-LMG-track</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3254,47 +3180,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>8</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-09-13 00:00</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-09-13 08:00</t>
-        </is>
+        <v>1.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COR-MTUR-SNDI</t>
+          <t>COR-KXB-MNV</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COR-MTUR-SNDI-track</t>
+          <t>COR-KXB-MNV-track</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3304,32 +3220,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COR-MURI-SLF</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COR-MURI-SLF-track</t>
+          <t>COR-RPK-GGD-track</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3344,22 +3260,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COR-SND-BLNG</t>
+          <t>COR-CXA-NRNR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COR-SND-BLNG-track</t>
+          <t>COR-CXA-NRNR-track</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3369,87 +3285,87 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2.15</v>
+        <v>4.88</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30</t>
+          <t>2026-09-21 14:15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-09-18 13:39</t>
+          <t>2026-09-21 19:07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COR-BALU-SLZ</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>COR-BALU-SLZ-track</t>
+          <t>COR-KKRD-VYA-track</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COR-KXB-MNV</t>
+          <t>COR-BOKO-DPRA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COR-KXB-MNV-track</t>
+          <t>COR-BOKO-DPRA-track</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3459,22 +3375,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>4.57</v>
+        <v>2.24</v>
+      </c>
+      <c r="H77" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COR-PRP-KEH</t>
+          <t>COR-KAMG-SMTA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COR-PRP-KEH-track</t>
+          <t>COR-KAMG-SMTA-track</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3484,75 +3403,82 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H78" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COR-CXA-NRNR</t>
+          <t>COR-TKC-PNB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COR-CXA-NRNR-track</t>
+          <t>COR-TKC-PNB-track</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>3.62</v>
+        <v>4.28</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-16 11:30</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:46</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COR-SRVN-MGF</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>COR-SRVN-MGF-track</t>
+          <t>COR-KKRD-VYA-track</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3562,7 +3488,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3571,141 +3497,158 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-09-13 23:15</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>2026-09-14 03:10</t>
-        </is>
+        <v>2.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COR-BHGP-LIR</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COR-BHGP-LIR-track</t>
+          <t>COR-BSR-JCNR-track</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G81" t="n">
         <v>4.02</v>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:00</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>COR-CTRD-TAV</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COR-CTRD-TAV-track</t>
+          <t>COR-DXG-BHNE-track</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>4.04</v>
+        <v>2.49</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:00</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:29</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COR-JLY-MQQ</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COR-JLY-MQQ-track</t>
+          <t>COR-SHIV-ALN-track</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>rail_wear</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="H83" t="n">
-        <v>15</v>
+        <v>1.66</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:30</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:09</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COR-KPPR-MGSJ</t>
+          <t>COR-PLSG-BSDR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COR-KPPR-MGSJ-track</t>
+          <t>COR-PLSG-BSDR-track</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3715,37 +3658,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:30</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-09-15 18:15</t>
-        </is>
+        <v>3.14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COR-JKI-MIM</t>
+          <t>COR-SVZ-BKSA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COR-JKI-MIM-track</t>
+          <t>COR-SVZ-BKSA-track</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3760,82 +3693,75 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:15</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:34</t>
-        </is>
+        <v>4.38</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>COR-AUI-SKEN</t>
+          <t>COR-SVZ-BKSA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COR-AUI-SKEN-track</t>
+          <t>COR-SVZ-BKSA-track</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>6.33</v>
+        <v>4.98</v>
+      </c>
+      <c r="H86" t="n">
+        <v>15</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-09-13 22:00</t>
+          <t>2026-09-16 22:30</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-09-14 04:19</t>
+          <t>2026-09-17 03:28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COR-BLGA-MYS</t>
+          <t>COR-PRTP-MTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COR-BLGA-MYS-track</t>
+          <t>COR-PRTP-MTC-track</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3850,37 +3776,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3.7</v>
+        <v>3.49</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-09-15 23:00</t>
+          <t>2026-09-14 22:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-09-16 02:42</t>
+          <t>2026-09-15 01:59</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>COR-NQH-JPE</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COR-NQH-JPE-track</t>
+          <t>COR-KDH-TGH-track</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3900,177 +3826,190 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>COR-PMT-RJP</t>
+          <t>COR-KRPU-MVF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>COR-PMT-RJP-track</t>
+          <t>COR-KRPU-MVF-track</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>7.24</v>
+        <v>3.96</v>
+      </c>
+      <c r="H89" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>COR-SMLG-ARK</t>
+          <t>COR-CRN-TTW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>COR-SMLG-ARK-track</t>
+          <t>COR-CRN-TTW-track</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3.51</v>
+        <v>1.9</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:00</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:54</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>COR-NKM-RNC</t>
+          <t>COR-TIS-GAG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>COR-NKM-RNC-track</t>
+          <t>COR-TIS-GAG-track</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-09-14 23:00</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2026-09-15 04:46</t>
-        </is>
+        <v>3.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>COR-PEI-VVN</t>
+          <t>COR-ISH-NOI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>COR-PEI-VVN-track</t>
+          <t>COR-ISH-NOI-track</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>weld_defect</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>5.58</v>
+        <v>1.78</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-19 10:30</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:16</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COR-CRQ-SRMN</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COR-CRQ-SRMN-track</t>
+          <t>COR-KDH-TGH-track</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4080,82 +4019,65 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:30</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2026-09-21 08:26</t>
-        </is>
+        <v>4.83</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>COR-NYP-DVR</t>
+          <t>COR-NIR-JGZ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COR-NYP-DVR-track</t>
+          <t>COR-NIR-JGZ-track</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>track_geometry_twist</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-09-20 01:00</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>2026-09-20 03:29</t>
-        </is>
+        <v>3.78</v>
+      </c>
+      <c r="H94" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>COR-RJT-KHDI</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COR-RJT-KHDI-track</t>
+          <t>COR-KKRD-VYA-track</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4165,127 +4087,120 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-09-16 14:00</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2026-09-16 17:45</t>
-        </is>
+        <v>3.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COR-SPD-UA</t>
+          <t>COR-BP-PTF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COR-SPD-UA-track</t>
+          <t>COR-BP-PTF-track</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>track_geometry_twist</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>5.97</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COR-JTTN-RWH</t>
+          <t>COR-DI-THK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COR-JTTN-RWH-track</t>
+          <t>COR-DI-THK-track</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>ballast_deficiency</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>7.45</v>
+        <v>4.9</v>
+      </c>
+      <c r="H97" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>COR-WDR-MZL</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COR-WDR-MZL-track</t>
+          <t>COR-KHDI-PDH-track</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>rail_fracture_risk</t>
+          <t>rail_wear</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4294,21 +4209,18 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H98" t="n">
-        <v>30</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COR-DMW-RDV</t>
+          <t>COR-PRTP-MTC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>COR-DMW-RDV-track</t>
+          <t>COR-PRTP-MTC-track</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4323,7 +4235,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4332,90 +4244,87 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>7.66</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>COR-KLMG-NVRD</t>
+          <t>COR-NAC-NYK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>COR-KLMG-NVRD-track</t>
+          <t>COR-NAC-NYK-track</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ballast_deficiency</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H100" t="n">
-        <v>30</v>
+        <v>2.34</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-12 22:30</t>
+          <t>2026-09-21 00:30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-09-13 02:25</t>
+          <t>2026-09-21 02:50</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COR-MUUA-BBW</t>
+          <t>COR-DHRY-HJI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COR-MUUA-BBW-track</t>
+          <t>COR-DHRY-HJI-track</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>weld_defect</t>
+          <t>rail_fracture_risk</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>5.11</v>
+        <v>4.41</v>
       </c>
     </row>
   </sheetData>
